--- a/stories/arbres/TREE-FAM-003.xlsx
+++ b/stories/arbres/TREE-FAM-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila est sous le pommier, avec papa. Maman est à la maison, tout près. Lila sent un malaise. Son ventre est serré. Elle a un peu peur. Papa dit : si on a peur ou un malaise, on raconte à papa ou maman.</t>
+          <t>Lila est sous le pommier, avec papa. Maman est à la maison, tout près. Lila sent un malaise. Son ventre est serré. Elle a un peu peur. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lila est sous le pommier, avec papa. Maman est à la maison, tout près. Lila sent un malaise. Son ventre est serré. Elle a un peu peur.
+papa|Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1514,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1543,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila joue avec Tom sous le pommier. Tom dit : c'est un secret. Lila sent un malaise. Elle a peur. Elle va vers papa. Elle raconte à papa. On raconte à papa ou maman.</t>
+          <t>Lila joue avec Tom sous le pommier. C'est un secret. Lila sent un malaise. Elle a peur. Elle va vers papa. Elle raconte à papa. On raconte à papa ou maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1681,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila joue avec Tom sous le pommier.
+enfant-m|C'est un secret.
+narrateur|Lila sent un malaise. Elle a peur. Elle va vers papa. Elle raconte à papa. On raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1864,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Un malaise, on raconte à papa ou maman ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2037,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On raconte à papa ou maman. Lila respire. Papa est là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2228,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2395,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lila et Tom ont les cubes. Le malaise est encore là. Lila a peur. Elle raconte à papa. Elle racontera à maman. Papa montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2586,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2753,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi Tom. Puis les cubes. Puis une pomme. Un ballon s'immobilise. Lila dit merci à papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2920,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3087,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lila s'arrête près de un yaourt. les cubes est rangé. Ça sent le pain chaud. Lila marche près de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3254,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3421,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lila se souvient de Tom. Et de les cubes. Et de un morceau de pain. Un galet est encore chaud. Maman n'est pas loin. Lila les rejoint. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3588,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3617,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Lila et Tom ont le livre. Le malaise est encore là. Lila a peur. Elle raconte à papa. Elle racontera à maman. Papa dit : je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+          <t>Lila et Tom ont le livre. Le malaise est encore là. Lila a peur. Elle raconte à papa. Elle racontera à maman. Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3755,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lila et Tom ont le livre. Le malaise est encore là. Lila a peur. Elle raconte à papa. Elle racontera à maman.
+papa|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3947,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4114,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec une pomme. Après le livre. Près de Tom. Lila s'arrête. Le vent est doux. Lila boit une gorgée d'eau. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4281,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4448,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lila range le livre. un yaourt reste près de Tom. Un linge sèche à l'air. Lila caresse le doudou. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4615,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4523,7 +4644,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. On souffle doucement. Lila ferme le sac. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+          <t>Un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. On souffle doucement. Lila ferme le sac. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4661,6 +4782,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. On souffle doucement. Lila ferme le sac. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4949,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5116,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lila et Tom ont la dînette. Le malaise est encore là. Lila a peur. Elle raconte à papa. Elle racontera à maman. Papa reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5307,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5474,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint une pomme. la dînette est rangé. Tom est fini. L'eau coule, tout petit bruit. Lila raccroche un linge. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5641,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5808,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de un yaourt. Lila pose la dînette. Tom est derrière. Il y a des miettes sur la table. Lila pose la dînette à sa place. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5975,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5843,7 +6004,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Lila montre un morceau de pain. Papa a vu Tom. Et la dînette. Le savon sent bon. Lila dit : j'ai appris. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+          <t>Lila montre un morceau de pain. Papa a vu Tom. Et la dînette. Le savon sent bon. J'ai appris. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5981,6 +6142,13 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lila montre un morceau de pain. Papa a vu Tom. Et la dînette. Le savon sent bon.
+enfant-f|J'ai appris. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman.
+narrateur|Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6311,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6340,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lila joue avec Léa. Léa dit : ne dis rien. Lila a le ventre serré. C'est un malaise. Elle a peur. Elle va le dire à papa. Plus tard, elle le dira aussi à maman.</t>
+          <t>Lila joue avec Léa. Ne dis rien. Lila a le ventre serré. C'est un malaise. Elle a peur. Elle va le dire à papa. Plus tard, elle le dira aussi à maman.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6478,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lila joue avec Léa.
+enfant-f|Ne dis rien.
+narrateur|Lila a le ventre serré. C'est un malaise. Elle a peur. Elle va le dire à papa. Plus tard, elle le dira aussi à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6665,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Si on a peur, on fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6838,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On raconte à papa ou maman. Lila retient le geste. Papa sourit. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7029,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6863,7 +7058,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Lila et Léa ont les cubes. Lila dit son malaise. Elle a peur. Elle raconte à papa ou maman. Papa l'écoute. Papa dit : je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+          <t>Lila et Léa ont les cubes. Lila dit son malaise. Elle a peur. Elle raconte à papa ou maman. Papa l'écoute. Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7001,6 +7196,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lila et Léa ont les cubes. Lila dit son malaise. Elle a peur. Elle raconte à papa ou maman. Papa l'écoute.
+papa|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7388,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7555,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi Léa. Puis les cubes. Puis une pomme. Les chaussures font toc toc. Lila écoute papa encore une fois. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7722,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7889,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lila s'arrête près de un yaourt. les cubes est rangé. Un vélo passe au loin. Lila serre la main de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8056,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8223,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lila se souvient de Léa. Et de les cubes. Et de un morceau de pain. On se tient la main. Lila tend un morceau de pain à maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8390,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8557,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lila et Léa ont le livre. Lila dit son malaise. Elle a peur. Elle raconte à papa ou maman. Papa l'écoute. Papa reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8748,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8915,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec une pomme. Après le livre. Près de Léa. Lila s'arrête. Une chaussette est encore sablée. Lila plie un pull. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9082,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9249,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lila range le livre. un yaourt reste près de Léa. Un ruban reste dans la poche. Lila essuie ses mains. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9416,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9179,7 +9445,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. On rit un peu. Lila prend la main de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+          <t>Un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. On rit un peu. Lila prend la main de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9317,6 +9583,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. On rit un peu. Lila prend la main de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9750,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9917,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lila et Léa ont la dînette. Lila dit son malaise. Elle a peur. Elle raconte à papa ou maman. Papa l'écoute. Papa montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10108,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10275,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint une pomme. la dînette est rangé. Léa est fini. Un panier est posé sur le banc. Lila enfile ses chaussons. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10442,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10609,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de un yaourt. Lila pose la dînette. Léa est derrière. Une cloche tinte, tout loin. Lila ferme la porte, tout doux. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10776,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10943,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lila montre un morceau de pain. Papa a vu Léa. Et la dînette. La lumière est claire. Lila range la tasse. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11110,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10961,6 +11277,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lila joue avec Sami. Un bruit étrange vient du chemin. Lila a peur. Elle sent un malaise. Elle raconte à papa. Papa l'écoute. On raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11458,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On garde le malaise, ou on raconte ?</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11631,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On raconte à papa ou maman. Lila hoche la tête. On continue, avec papa. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11491,6 +11822,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11653,6 +11989,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lila et Sami ont les cubes. Un bruit revient. Lila a peur. Elle sent un malaise. Elle raconte à papa ou maman. Papa reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11839,6 +12180,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12001,6 +12347,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi Sami. Puis les cubes. Puis une pomme. Une pomme brille un peu. Lila répète tout bas le geste. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12163,6 +12514,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12325,6 +12681,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lila s'arrête près de un yaourt. les cubes est rangé. On attend son tour. Lila souffle, puis sourit à papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12487,6 +12848,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12649,6 +13015,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lila se souvient de Sami. Et de les cubes. Et de un morceau de pain. Un chat miaule une fois. Lila range Sami dans sa tête, comme un souvenir. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12811,6 +13182,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12973,6 +13349,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lila et Sami ont le livre. Un bruit revient. Lila a peur. Elle sent un malaise. Elle raconte à papa ou maman. Papa montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13159,6 +13540,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13321,6 +13707,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec une pomme. Après le livre. Près de Sami. Lila s'arrête. Une feuille tombe. Lila montre une pomme à papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13483,6 +13874,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13645,6 +14041,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lila range le livre. un yaourt reste près de Sami. On dit merci. Lila pose sa tête un moment. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13807,6 +14208,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13831,7 +14237,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. On entend un oiseau. Lila chuchote : c'est fini. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+          <t>Un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. On entend un oiseau. Lila chuchote : c'est fini. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13969,6 +14375,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. On entend un oiseau. Lila chuchote : c'est fini. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14131,6 +14542,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14155,7 +14571,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Lila et Sami ont la dînette. Un bruit revient. Lila a peur. Elle sent un malaise. Elle raconte à papa ou maman. Papa dit : je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+          <t>Lila et Sami ont la dînette. Un bruit revient. Lila a peur. Elle sent un malaise. Elle raconte à papa ou maman. Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14293,6 +14709,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lila et Sami ont la dînette. Un bruit revient. Lila a peur. Elle sent un malaise. Elle raconte à papa ou maman.
+papa|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14479,6 +14901,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14641,6 +15068,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint une pomme. la dînette est rangé. Sami est fini. On écoute jusqu'au bout. Lila range encore un peu, près de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14803,6 +15235,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14965,6 +15402,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de un yaourt. Lila pose la dînette. Sami est derrière. On range un objet. Lila sourit. Papa sourit aussi. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15127,6 +15569,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15289,6 +15736,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lila montre un morceau de pain. Papa a vu Sami. Et la dînette. Une tasse cliquette. Lila s'assoit près de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15451,6 +15903,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15469,7 +15926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15486,6 +15943,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-FAM-003.xlsx
+++ b/stories/arbres/TREE-FAM-003.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 papa|Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1519,6 +1525,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1688,6 +1695,7 @@
 narrateur|Lila sent un malaise. Elle a peur. Elle va vers papa. Elle raconte à papa. On raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1871,6 +1879,7 @@
           <t>narrateur|Un malaise, on raconte à papa ou maman ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2042,6 +2051,7 @@
           <t>narrateur|Oui. On raconte à papa ou maman. Lila respire. Papa est là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2233,6 +2243,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2400,6 +2411,7 @@
           <t>narrateur|Lila et Tom ont les cubes. Le malaise est encore là. Lila a peur. Elle raconte à papa. Elle racontera à maman. Papa montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2591,6 +2603,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2758,6 +2771,7 @@
           <t>narrateur|Lila a choisi Tom. Puis les cubes. Puis une pomme. Un ballon s'immobilise. Lila dit merci à papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2925,6 +2939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3092,6 +3107,7 @@
           <t>narrateur|Lila s'arrête près de un yaourt. les cubes est rangé. Ça sent le pain chaud. Lila marche près de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3259,6 +3275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3426,6 +3443,7 @@
           <t>narrateur|Lila se souvient de Tom. Et de les cubes. Et de un morceau de pain. Un galet est encore chaud. Maman n'est pas loin. Lila les rejoint. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3593,6 +3611,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3761,6 +3780,7 @@
 papa|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3952,6 +3972,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4119,6 +4140,7 @@
           <t>narrateur|Avec une pomme. Après le livre. Près de Tom. Lila s'arrête. Le vent est doux. Lila boit une gorgée d'eau. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4286,6 +4308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4453,6 +4476,7 @@
           <t>narrateur|Lila range le livre. un yaourt reste près de Tom. Un linge sèche à l'air. Lila caresse le doudou. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4620,6 +4644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4787,6 +4812,7 @@
           <t>narrateur|Un morceau de pain est là. le livre aussi. Tom reste dans le souvenir. On souffle doucement. Lila ferme le sac. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4954,6 +4980,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5121,6 +5148,7 @@
           <t>narrateur|Lila et Tom ont la dînette. Le malaise est encore là. Lila a peur. Elle raconte à papa. Elle racontera à maman. Papa reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5312,6 +5340,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5479,6 +5508,7 @@
           <t>narrateur|Lila rejoint une pomme. la dînette est rangé. Tom est fini. L'eau coule, tout petit bruit. Lila raccroche un linge. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5646,6 +5676,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5813,6 +5844,7 @@
           <t>narrateur|Près de un yaourt. Lila pose la dînette. Tom est derrière. Il y a des miettes sur la table. Lila pose la dînette à sa place. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5980,6 +6012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6149,6 +6182,7 @@
 narrateur|Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6316,6 +6350,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6485,6 +6520,7 @@
 narrateur|Lila a le ventre serré. C'est un malaise. Elle a peur. Elle va le dire à papa. Plus tard, elle le dira aussi à maman.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6672,6 +6708,7 @@
           <t>narrateur|Si on a peur, on fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6843,6 +6880,7 @@
           <t>narrateur|Oui. On raconte à papa ou maman. Lila retient le geste. Papa sourit. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7034,6 +7072,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7202,6 +7241,7 @@
 papa|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7393,6 +7433,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7560,6 +7601,7 @@
           <t>narrateur|Lila a choisi Léa. Puis les cubes. Puis une pomme. Les chaussures font toc toc. Lila écoute papa encore une fois. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7727,6 +7769,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7894,6 +7937,7 @@
           <t>narrateur|Lila s'arrête près de un yaourt. les cubes est rangé. Un vélo passe au loin. Lila serre la main de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8061,6 +8105,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8228,6 +8273,7 @@
           <t>narrateur|Lila se souvient de Léa. Et de les cubes. Et de un morceau de pain. On se tient la main. Lila tend un morceau de pain à maman. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8395,6 +8441,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8562,6 +8609,7 @@
           <t>narrateur|Lila et Léa ont le livre. Lila dit son malaise. Elle a peur. Elle raconte à papa ou maman. Papa l'écoute. Papa reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8753,6 +8801,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8920,6 +8969,7 @@
           <t>narrateur|Avec une pomme. Après le livre. Près de Léa. Lila s'arrête. Une chaussette est encore sablée. Lila plie un pull. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9087,6 +9137,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9254,6 +9305,7 @@
           <t>narrateur|Lila range le livre. un yaourt reste près de Léa. Un ruban reste dans la poche. Lila essuie ses mains. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9421,6 +9473,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9588,6 +9641,7 @@
           <t>narrateur|Un morceau de pain est là. le livre aussi. Léa reste dans le souvenir. On rit un peu. Lila prend la main de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9755,6 +9809,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9922,6 +9977,7 @@
           <t>narrateur|Lila et Léa ont la dînette. Lila dit son malaise. Elle a peur. Elle raconte à papa ou maman. Papa l'écoute. Papa montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10113,6 +10169,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10280,6 +10337,7 @@
           <t>narrateur|Lila rejoint une pomme. la dînette est rangé. Léa est fini. Un panier est posé sur le banc. Lila enfile ses chaussons. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10447,6 +10505,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10614,6 +10673,7 @@
           <t>narrateur|Près de un yaourt. Lila pose la dînette. Léa est derrière. Une cloche tinte, tout loin. Lila ferme la porte, tout doux. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10781,6 +10841,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10948,6 +11009,7 @@
           <t>narrateur|Lila montre un morceau de pain. Papa a vu Léa. Et la dînette. La lumière est claire. Lila range la tasse. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11115,6 +11177,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11282,6 +11345,7 @@
           <t>narrateur|Lila joue avec Sami. Un bruit étrange vient du chemin. Lila a peur. Elle sent un malaise. Elle raconte à papa. Papa l'écoute. On raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11465,6 +11529,7 @@
           <t>narrateur|On garde le malaise, ou on raconte ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11636,6 +11701,7 @@
           <t>narrateur|Oui. On raconte à papa ou maman. Lila hoche la tête. On continue, avec papa. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11827,6 +11893,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11994,6 +12061,7 @@
           <t>narrateur|Lila et Sami ont les cubes. Un bruit revient. Lila a peur. Elle sent un malaise. Elle raconte à papa ou maman. Papa reste tout près. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12185,6 +12253,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12352,6 +12421,7 @@
           <t>narrateur|Lila a choisi Sami. Puis les cubes. Puis une pomme. Une pomme brille un peu. Lila répète tout bas le geste. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12519,6 +12589,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12686,6 +12757,7 @@
           <t>narrateur|Lila s'arrête près de un yaourt. les cubes est rangé. On attend son tour. Lila souffle, puis sourit à papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12853,6 +12925,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13020,6 +13093,7 @@
           <t>narrateur|Lila se souvient de Sami. Et de les cubes. Et de un morceau de pain. Un chat miaule une fois. Lila range Sami dans sa tête, comme un souvenir. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13187,6 +13261,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13354,6 +13429,7 @@
           <t>narrateur|Lila et Sami ont le livre. Un bruit revient. Lila a peur. Elle sent un malaise. Elle raconte à papa ou maman. Papa montre le geste, lentement. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13545,6 +13621,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13712,6 +13789,7 @@
           <t>narrateur|Avec une pomme. Après le livre. Près de Sami. Lila s'arrête. Une feuille tombe. Lila montre une pomme à papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13879,6 +13957,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14046,6 +14125,7 @@
           <t>narrateur|Lila range le livre. un yaourt reste près de Sami. On dit merci. Lila pose sa tête un moment. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14213,6 +14293,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14380,6 +14461,7 @@
           <t>narrateur|Un morceau de pain est là. le livre aussi. Sami reste dans le souvenir. On entend un oiseau. Lila chuchote : c'est fini. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14547,6 +14629,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14715,6 +14798,7 @@
 papa|Je suis là. Si on a peur ou un malaise, on raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14906,6 +14990,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15073,6 +15158,7 @@
           <t>narrateur|Lila rejoint une pomme. la dînette est rangé. Sami est fini. On écoute jusqu'au bout. Lila range encore un peu, près de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15240,6 +15326,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15407,6 +15494,7 @@
           <t>narrateur|Près de un yaourt. Lila pose la dînette. Sami est derrière. On range un objet. Lila sourit. Papa sourit aussi. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15574,6 +15662,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15741,6 +15830,7 @@
           <t>narrateur|Lila montre un morceau de pain. Papa a vu Sami. Et la dînette. Une tasse cliquette. Lila s'assoit près de papa. Si on a peur ou un malaise, on raconte à papa ou maman. On va le dire. On raconte à papa ou maman. Lila dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15908,6 +15998,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15926,7 +16017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15950,6 +16041,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15964,7 +16069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16151,6 +16256,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
